--- a/apps/desktop/public/mau-nhap-thanh-tich.xlsx
+++ b/apps/desktop/public/mau-nhap-thanh-tich.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thành tích" sheetId="1" r:id="R04f137ab3acc414d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hướng dẫn" sheetId="2" r:id="Rdf67e6543068421b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thành tích" sheetId="1" r:id="R8496c137521b4589"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hướng dẫn" sheetId="2" r:id="Rb25153e05b154b5e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -402,7 +402,7 @@
     </x:row>
     <x:row r="2" ht="31" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>Mỗi dòng là một thành tích. Hệ thống chỉ ghép thành tích vào nhân viên bằng CCCD; CCCD không tồn tại sẽ bị từ chối.</x:v>
+        <x:v>Mỗi dòng là một thành tích. CCCD bắt buộc đúng 12 chữ số và được giữ dạng text; hệ thống chỉ ghép thành tích vào nhân viên bằng CCCD.</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -4565,7 +4565,7 @@
         <x:v>CCCD</x:v>
       </x:c>
       <x:c r="B4" s="32" t="str">
-        <x:v>Bắt buộc; phải tồn tại trong hồ sơ nhân viên; giữ dạng chuỗi 9–12 chữ số.</x:v>
+        <x:v>Bắt buộc; đúng 12 chữ số; phải tồn tại trong hồ sơ nhân viên; luôn giữ dạng text.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
